--- a/examples/排除清单_2026-08.xlsx
+++ b/examples/排除清单_2026-08.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,21 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +54,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,97 +428,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>事件摘要</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>国家</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>年份</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>月份</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>地点</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>死亡人数</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>受伤人数</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>袭击方式</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>袭击武器</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>袭击者</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>负责人/组织</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>信息来源URL</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>采集人/组别</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>录入日期</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>置信度</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>审核状态</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>关联知识点</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -516,12 +527,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>索马里国民军击毙至少30名青年党武装分子并抓获数人（安全部队反恐战果）</t>
+          <t>胡塞武装导弹袭击也门政府军营地，至少30名政府军士兵死亡、15人受伤</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>索马里</t>
+          <t>也门</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -531,43 +542,45 @@
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>拜多阿（Baidoa）</t>
+          <t>哈德拉毛省、马里布省</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>15</v>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>清剿</t>
+          <t>袭击</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>不明/其他</t>
+          <t>导弹</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>索马里国民军（国家力量）</t>
+          <t>胡塞武装</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>索马里国防部</t>
+          <t>胡塞武装（安萨鲁拉）</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://english.news.cn/africa/20260817/e353d1107bb340dd9b276d8e9ae3e277/c.html</t>
+          <t>https://www.aljazeera.com/news/2026/8/6/houthis-claim-to-have-killed-45-in-attacks-on-yemeni-government-forces</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>示例组</t>
+          <t>第七组</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -582,17 +595,12 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>已退回</t>
+          <t>反证 N4 已交战状态</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>反证 N5 反恐战果</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>[排除]反证 N5 反恐行动本身；原报道称 thwarted an early Monday attack，未给受害对象与伤亡，被挫败的图谋另建记录时落兜底</t>
+          <t>[排除]反证 N4：胡塞与也门政府军处于长期内战交战状态，袭击军营属双方交战行动，目标非『非战斗状态』。日期与数字均已确证，不是证据问题而是口径问题</t>
         </is>
       </c>
     </row>
